--- a/outputs_xlsx_solution/test_new4.2-wide.xlsx
+++ b/outputs_xlsx_solution/test_new4.2-wide.xlsx
@@ -65,7 +65,7 @@
     <t>addi X4, X0, 4</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fld F1, 0(X1)</t>
@@ -74,10 +74,10 @@
     <t>fadd F2, F1, F1</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fadd F3, F1, F1</t>
@@ -86,6 +86,9 @@
     <t>fmul F3, F1, F1</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F3</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>bne X5, X0, 28</t>
   </si>
   <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
     <t>fsd F2, 200(X0)</t>
   </si>
   <si>
@@ -113,13 +119,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -594,6 +618,12 @@
       <c r="AM1">
         <v>36</v>
       </c>
+      <c r="AN1">
+        <v>37</v>
+      </c>
+      <c r="AO1">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -615,7 +645,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -638,10 +668,10 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -664,10 +694,10 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -690,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +749,7 @@
         <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -739,19 +769,19 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -771,19 +801,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -803,22 +833,22 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +859,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -838,19 +868,19 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -861,7 +891,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -876,7 +906,7 @@
         <v>13</v>
       </c>
       <c r="Q11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -896,16 +926,16 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M12" t="s">
         <v>13</v>
       </c>
-      <c r="Q12" t="s">
-        <v>13</v>
+      <c r="R12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -916,7 +946,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -930,8 +960,8 @@
       <c r="L13" t="s">
         <v>13</v>
       </c>
-      <c r="Q13" t="s">
-        <v>13</v>
+      <c r="R13" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -942,7 +972,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -951,16 +981,16 @@
         <v>7</v>
       </c>
       <c r="L14" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N14" t="s">
         <v>13</v>
       </c>
-      <c r="Q14" t="s">
-        <v>13</v>
+      <c r="S14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -971,7 +1001,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -980,16 +1010,16 @@
         <v>7</v>
       </c>
       <c r="L15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O15" t="s">
         <v>13</v>
       </c>
-      <c r="Q15" t="s">
-        <v>13</v>
+      <c r="S15" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1009,19 +1039,22 @@
         <v>7</v>
       </c>
       <c r="Q16" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U16" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="V16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1032,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O17" t="s">
         <v>5</v>
@@ -1041,19 +1074,22 @@
         <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>10</v>
-      </c>
-      <c r="U17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X17" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1064,7 +1100,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P18" t="s">
         <v>5</v>
@@ -1078,8 +1114,8 @@
       <c r="S18" t="s">
         <v>13</v>
       </c>
-      <c r="X18" t="s">
-        <v>13</v>
+      <c r="Z18" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1099,16 +1135,16 @@
         <v>7</v>
       </c>
       <c r="R19" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T19" t="s">
         <v>13</v>
       </c>
-      <c r="X19" t="s">
-        <v>13</v>
+      <c r="AA19" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -1119,7 +1155,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="s">
         <v>5</v>
@@ -1133,8 +1169,8 @@
       <c r="T20" t="s">
         <v>13</v>
       </c>
-      <c r="X20" t="s">
-        <v>13</v>
+      <c r="AA20" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1145,7 +1181,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q21" t="s">
         <v>5</v>
@@ -1154,126 +1190,129 @@
         <v>7</v>
       </c>
       <c r="S21" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U21" t="s">
         <v>13</v>
       </c>
-      <c r="X21" t="s">
-        <v>13</v>
+      <c r="AB21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
+      <c r="R22" t="s">
+        <v>5</v>
       </c>
       <c r="S22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T22" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="U22" t="s">
         <v>10</v>
       </c>
       <c r="V22" t="s">
-        <v>14</v>
-      </c>
-      <c r="W22" t="s">
-        <v>14</v>
-      </c>
-      <c r="X22" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="S23" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" t="s">
+        <v>7</v>
+      </c>
+      <c r="U23" t="s">
+        <v>17</v>
+      </c>
+      <c r="V23" t="s">
+        <v>10</v>
+      </c>
+      <c r="W23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="S23" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" t="s">
-        <v>7</v>
-      </c>
-      <c r="U23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>14</v>
-      </c>
       <c r="AA23" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="s">
         <v>14</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
+      <c r="S24" t="s">
+        <v>5</v>
+      </c>
       <c r="T24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U24" t="s">
-        <v>7</v>
-      </c>
-      <c r="V24" t="s">
-        <v>10</v>
-      </c>
-      <c r="W24" t="s">
-        <v>14</v>
-      </c>
-      <c r="X24" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>10</v>
       </c>
       <c r="AD24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T25" t="s">
         <v>5</v>
@@ -1282,53 +1321,53 @@
         <v>7</v>
       </c>
       <c r="V25" t="s">
+        <v>17</v>
+      </c>
+      <c r="W25" t="s">
         <v>10</v>
       </c>
       <c r="X25" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y25" t="s">
         <v>13</v>
       </c>
       <c r="AD25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="T26" t="s">
+        <v>5</v>
       </c>
       <c r="U26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V26" t="s">
-        <v>7</v>
-      </c>
-      <c r="W26" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="s">
         <v>13</v>
       </c>
-      <c r="AD26" t="s">
-        <v>13</v>
+      <c r="AE26" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -1340,488 +1379,602 @@
         <v>7</v>
       </c>
       <c r="W27" t="s">
+        <v>17</v>
+      </c>
+      <c r="X27" t="s">
         <v>10</v>
       </c>
       <c r="Y27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="U28" t="s">
+        <v>5</v>
+      </c>
+      <c r="V28" t="s">
+        <v>7</v>
       </c>
       <c r="W28" t="s">
-        <v>5</v>
-      </c>
-      <c r="X28" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y28" t="s">
         <v>10</v>
       </c>
       <c r="Z28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="V29" t="s">
+        <v>5</v>
       </c>
       <c r="W29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>13</v>
       </c>
       <c r="AF29" t="s">
         <v>14</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="W30" t="s">
+        <v>5</v>
       </c>
       <c r="X30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>40</v>
-      </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="W31" t="s">
+        <v>5</v>
       </c>
       <c r="X31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y31" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>10</v>
       </c>
       <c r="AH31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
       </c>
+      <c r="X32" t="s">
+        <v>5</v>
+      </c>
       <c r="Y32" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z32" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="s">
         <v>10</v>
       </c>
       <c r="AB32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC32" t="s">
         <v>13</v>
       </c>
       <c r="AH32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="X33" t="s">
+        <v>5</v>
       </c>
       <c r="Y33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA33" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB33" t="s">
         <v>10</v>
       </c>
       <c r="AC33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>7</v>
       </c>
       <c r="AA34" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AB34" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC34" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>7</v>
       </c>
       <c r="AA35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC35" t="s">
         <v>10</v>
       </c>
-      <c r="AI35" t="s">
-        <v>14</v>
+      <c r="AD35" t="s">
+        <v>13</v>
       </c>
       <c r="AJ35" t="s">
         <v>14</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>7</v>
       </c>
       <c r="AB36" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AD36" t="s">
         <v>10</v>
       </c>
       <c r="AE36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>13</v>
+        <v>13</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>5</v>
       </c>
       <c r="AB37" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC37" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD37" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE37" t="s">
         <v>10</v>
       </c>
       <c r="AF37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AG37" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL37" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>7</v>
       </c>
       <c r="AC38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>10</v>
       </c>
       <c r="AL38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>5</v>
       </c>
       <c r="AC39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD39" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AE39" t="s">
         <v>10</v>
       </c>
-      <c r="AG39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH39" t="s">
+      <c r="AF39" t="s">
         <v>13</v>
       </c>
       <c r="AL39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>7</v>
       </c>
       <c r="AD40" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF40" t="s">
         <v>10</v>
       </c>
-      <c r="AH40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>13</v>
+      <c r="AG40" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
+      <c r="AI44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO44" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_new4.2-wide.xlsx
+++ b/outputs_xlsx_solution/test_new4.2-wide.xlsx
@@ -68,6 +68,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fld F1, 0(X1)</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -645,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -665,13 +671,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -691,13 +697,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -717,13 +723,16 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -746,10 +755,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -760,7 +769,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -769,7 +778,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
@@ -781,7 +790,7 @@
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +801,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -801,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
@@ -813,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +833,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -833,7 +842,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
         <v>10</v>
@@ -848,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -859,7 +868,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -868,7 +877,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
         <v>10</v>
@@ -880,7 +889,7 @@
         <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -891,7 +900,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -903,10 +912,10 @@
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -917,7 +926,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
@@ -926,16 +935,16 @@
         <v>7</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" t="s">
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -946,7 +955,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -958,10 +967,10 @@
         <v>10</v>
       </c>
       <c r="L13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -972,7 +981,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -981,16 +990,16 @@
         <v>7</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
       </c>
       <c r="N14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1001,7 +1010,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -1010,16 +1019,16 @@
         <v>7</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
         <v>10</v>
       </c>
       <c r="O15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1030,7 +1039,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" t="s">
         <v>5</v>
@@ -1039,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="Q16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -1054,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="V16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1065,7 +1074,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O17" t="s">
         <v>5</v>
@@ -1074,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="Q17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V17" t="s">
         <v>10</v>
@@ -1086,10 +1095,10 @@
         <v>10</v>
       </c>
       <c r="Y17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1100,7 +1109,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
         <v>5</v>
@@ -1112,10 +1121,10 @@
         <v>10</v>
       </c>
       <c r="S18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1126,7 +1135,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P19" t="s">
         <v>5</v>
@@ -1135,16 +1144,16 @@
         <v>7</v>
       </c>
       <c r="R19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S19" t="s">
         <v>10</v>
       </c>
       <c r="T19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1155,7 +1164,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="s">
         <v>5</v>
@@ -1167,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="T20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1181,7 +1190,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q21" t="s">
         <v>5</v>
@@ -1190,16 +1199,16 @@
         <v>7</v>
       </c>
       <c r="S21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T21" t="s">
         <v>10</v>
       </c>
       <c r="U21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1210,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R22" t="s">
         <v>5</v>
@@ -1219,16 +1228,16 @@
         <v>7</v>
       </c>
       <c r="T22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U22" t="s">
         <v>10</v>
       </c>
       <c r="V22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1239,7 +1248,7 @@
         <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S23" t="s">
         <v>5</v>
@@ -1248,7 +1257,7 @@
         <v>7</v>
       </c>
       <c r="U23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V23" t="s">
         <v>10</v>
@@ -1263,13 +1272,13 @@
         <v>10</v>
       </c>
       <c r="Z23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1280,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S24" t="s">
         <v>5</v>
@@ -1289,7 +1298,7 @@
         <v>7</v>
       </c>
       <c r="U24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s">
         <v>10</v>
@@ -1301,7 +1310,7 @@
         <v>10</v>
       </c>
       <c r="AD24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1312,7 +1321,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T25" t="s">
         <v>5</v>
@@ -1321,16 +1330,16 @@
         <v>7</v>
       </c>
       <c r="V25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W25" t="s">
         <v>10</v>
       </c>
       <c r="X25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1341,7 +1350,7 @@
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T26" t="s">
         <v>5</v>
@@ -1350,16 +1359,16 @@
         <v>7</v>
       </c>
       <c r="V26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X26" t="s">
         <v>10</v>
       </c>
       <c r="Y26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1370,7 +1379,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U27" t="s">
         <v>5</v>
@@ -1379,16 +1388,16 @@
         <v>7</v>
       </c>
       <c r="W27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X27" t="s">
         <v>10</v>
       </c>
       <c r="Y27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1399,7 +1408,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U28" t="s">
         <v>5</v>
@@ -1408,16 +1417,16 @@
         <v>7</v>
       </c>
       <c r="W28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="s">
         <v>10</v>
       </c>
       <c r="Z28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1428,7 +1437,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V29" t="s">
         <v>5</v>
@@ -1437,16 +1446,16 @@
         <v>7</v>
       </c>
       <c r="X29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z29" t="s">
         <v>10</v>
       </c>
       <c r="AA29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1457,7 +1466,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W30" t="s">
         <v>5</v>
@@ -1466,7 +1475,10 @@
         <v>7</v>
       </c>
       <c r="Y30" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>11</v>
       </c>
       <c r="AA30" t="s">
         <v>10</v>
@@ -1481,10 +1493,10 @@
         <v>10</v>
       </c>
       <c r="AE30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1507,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W31" t="s">
         <v>5</v>
@@ -1504,7 +1516,7 @@
         <v>7</v>
       </c>
       <c r="Y31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="s">
         <v>10</v>
@@ -1516,7 +1528,7 @@
         <v>10</v>
       </c>
       <c r="AH31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1527,7 +1539,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X32" t="s">
         <v>5</v>
@@ -1536,16 +1548,16 @@
         <v>7</v>
       </c>
       <c r="Z32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="s">
         <v>10</v>
       </c>
       <c r="AB32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1556,7 +1568,7 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X33" t="s">
         <v>5</v>
@@ -1565,16 +1577,16 @@
         <v>7</v>
       </c>
       <c r="Z33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB33" t="s">
         <v>10</v>
       </c>
       <c r="AC33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -1585,7 +1597,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s">
         <v>5</v>
@@ -1594,16 +1606,16 @@
         <v>7</v>
       </c>
       <c r="AA34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB34" t="s">
         <v>10</v>
       </c>
       <c r="AC34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1614,7 +1626,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y35" t="s">
         <v>5</v>
@@ -1623,16 +1635,16 @@
         <v>7</v>
       </c>
       <c r="AA35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC35" t="s">
         <v>10</v>
       </c>
       <c r="AD35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1643,7 +1655,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z36" t="s">
         <v>5</v>
@@ -1652,16 +1664,16 @@
         <v>7</v>
       </c>
       <c r="AB36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD36" t="s">
         <v>10</v>
       </c>
       <c r="AE36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1684,7 @@
         <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="s">
         <v>5</v>
@@ -1681,7 +1693,10 @@
         <v>7</v>
       </c>
       <c r="AC37" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>11</v>
       </c>
       <c r="AE37" t="s">
         <v>10</v>
@@ -1696,10 +1711,10 @@
         <v>10</v>
       </c>
       <c r="AI37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1710,7 +1725,7 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="s">
         <v>5</v>
@@ -1719,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="AC38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI38" t="s">
         <v>10</v>
@@ -1731,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AL38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1742,7 +1757,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB39" t="s">
         <v>5</v>
@@ -1751,16 +1766,16 @@
         <v>7</v>
       </c>
       <c r="AD39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE39" t="s">
         <v>10</v>
       </c>
       <c r="AF39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -1771,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB40" t="s">
         <v>5</v>
@@ -1780,16 +1795,16 @@
         <v>7</v>
       </c>
       <c r="AD40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF40" t="s">
         <v>10</v>
       </c>
       <c r="AG40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1800,7 +1815,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="s">
         <v>5</v>
@@ -1809,16 +1824,16 @@
         <v>7</v>
       </c>
       <c r="AE41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF41" t="s">
         <v>10</v>
       </c>
       <c r="AG41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1829,7 +1844,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC42" t="s">
         <v>5</v>
@@ -1838,16 +1853,16 @@
         <v>7</v>
       </c>
       <c r="AE42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG42" t="s">
         <v>10</v>
       </c>
       <c r="AH42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,7 +1873,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD43" t="s">
         <v>5</v>
@@ -1867,16 +1882,16 @@
         <v>7</v>
       </c>
       <c r="AF43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH43" t="s">
         <v>10</v>
       </c>
       <c r="AI43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -1887,7 +1902,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI44" t="s">
         <v>5</v>
@@ -1896,21 +1911,21 @@
         <v>7</v>
       </c>
       <c r="AK44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL44" t="s">
         <v>10</v>
       </c>
       <c r="AM44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
@@ -1918,7 +1933,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -1926,15 +1941,15 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -1942,39 +1957,55 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
